--- a/planilha fechamento.xlsx
+++ b/planilha fechamento.xlsx
@@ -304,7 +304,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:G77"/>
+  <dimension ref="A1:G198"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="11.53515625" defaultRowHeight="12.75" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="20.26" customWidth="1" style="4" min="1" max="1"/>
@@ -3126,39 +3126,4516 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" t="inlineStr">
+      <c r="A77" s="4" t="inlineStr">
         <is>
           <t>Dra. Nina Caldeira</t>
         </is>
       </c>
-      <c r="B77" t="inlineStr">
+      <c r="B77" s="4" t="inlineStr">
         <is>
           <t>618.96</t>
         </is>
       </c>
-      <c r="C77" t="inlineStr">
+      <c r="C77" s="4" t="inlineStr">
         <is>
           <t>903.158.764-84</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr">
+      <c r="D77" s="4" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="E77" t="inlineStr">
+      <c r="E77" s="4" t="inlineStr">
         <is>
           <t>Erro ao coletar</t>
         </is>
       </c>
-      <c r="F77" t="inlineStr">
+      <c r="F77" s="4" t="inlineStr">
         <is>
           <t>01/05/2026</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr">
+      <c r="G77" s="4" t="inlineStr">
         <is>
           <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="4" t="inlineStr">
+        <is>
+          <t>Noah da Mota</t>
+        </is>
+      </c>
+      <c r="B78" s="4" t="inlineStr">
+        <is>
+          <t>747.91</t>
+        </is>
+      </c>
+      <c r="C78" s="4" t="inlineStr">
+        <is>
+          <t>472.963.815-82</t>
+        </is>
+      </c>
+      <c r="D78" s="4" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="E78" s="4" t="inlineStr">
+        <is>
+          <t>Pago</t>
+        </is>
+      </c>
+      <c r="F78" s="4" t="inlineStr">
+        <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="G78" s="4" t="inlineStr">
+        <is>
+          <t>CARTÃO</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="4" t="inlineStr">
+        <is>
+          <t>Carlos Eduardo Santos</t>
+        </is>
+      </c>
+      <c r="B79" s="4" t="inlineStr">
+        <is>
+          <t>123.2</t>
+        </is>
+      </c>
+      <c r="C79" s="4" t="inlineStr">
+        <is>
+          <t>231.659.708-40</t>
+        </is>
+      </c>
+      <c r="D79" s="4" t="inlineStr">
+        <is>
+          <t>07/12/2025</t>
+        </is>
+      </c>
+      <c r="E79" s="4" t="inlineStr">
+        <is>
+          <t>Pago</t>
+        </is>
+      </c>
+      <c r="F79" s="4" t="inlineStr">
+        <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="G79" s="4" t="inlineStr">
+        <is>
+          <t>CARTÃO</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="4" t="inlineStr">
+        <is>
+          <t>Dr. Felipe Farias</t>
+        </is>
+      </c>
+      <c r="B80" s="4" t="inlineStr">
+        <is>
+          <t>285.56</t>
+        </is>
+      </c>
+      <c r="C80" s="4" t="inlineStr">
+        <is>
+          <t>487.039.126-04</t>
+        </is>
+      </c>
+      <c r="D80" s="4" t="inlineStr">
+        <is>
+          <t>07/02/2026</t>
+        </is>
+      </c>
+      <c r="E80" s="4" t="inlineStr">
+        <is>
+          <t>Pago</t>
+        </is>
+      </c>
+      <c r="F80" s="4" t="inlineStr">
+        <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="G80" s="4" t="inlineStr">
+        <is>
+          <t>CARTÃO</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="4" t="inlineStr">
+        <is>
+          <t>Luigi Barros</t>
+        </is>
+      </c>
+      <c r="B81" s="4" t="inlineStr">
+        <is>
+          <t>349.87</t>
+        </is>
+      </c>
+      <c r="C81" s="4" t="inlineStr">
+        <is>
+          <t>179.432.680-40</t>
+        </is>
+      </c>
+      <c r="D81" s="4" t="inlineStr">
+        <is>
+          <t>29/06/2025</t>
+        </is>
+      </c>
+      <c r="E81" s="4" t="inlineStr">
+        <is>
+          <t>Pago</t>
+        </is>
+      </c>
+      <c r="F81" s="4" t="inlineStr">
+        <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="G81" s="4" t="inlineStr">
+        <is>
+          <t>CARTÃO</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="4" t="inlineStr">
+        <is>
+          <t>Stella da Luz</t>
+        </is>
+      </c>
+      <c r="B82" s="4" t="inlineStr">
+        <is>
+          <t>449.42</t>
+        </is>
+      </c>
+      <c r="C82" s="4" t="inlineStr">
+        <is>
+          <t>821.074.653-71</t>
+        </is>
+      </c>
+      <c r="D82" s="4" t="inlineStr">
+        <is>
+          <t>16/07/2024</t>
+        </is>
+      </c>
+      <c r="E82" s="4" t="inlineStr">
+        <is>
+          <t>Pago</t>
+        </is>
+      </c>
+      <c r="F82" s="4" t="inlineStr">
+        <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="G82" s="4" t="inlineStr">
+        <is>
+          <t>CARTÃO</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="4" t="inlineStr">
+        <is>
+          <t>Elisa da Cunha</t>
+        </is>
+      </c>
+      <c r="B83" s="4" t="inlineStr">
+        <is>
+          <t>655.34</t>
+        </is>
+      </c>
+      <c r="C83" s="4" t="inlineStr">
+        <is>
+          <t>281.597.640-49</t>
+        </is>
+      </c>
+      <c r="D83" s="4" t="inlineStr">
+        <is>
+          <t>07/05/2024</t>
+        </is>
+      </c>
+      <c r="E83" s="4" t="inlineStr">
+        <is>
+          <t>Pago</t>
+        </is>
+      </c>
+      <c r="F83" s="4" t="inlineStr">
+        <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="G83" s="4" t="inlineStr">
+        <is>
+          <t>CARTÃO</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="4" t="inlineStr">
+        <is>
+          <t>Rodrigo Fernandes</t>
+        </is>
+      </c>
+      <c r="B84" s="4" t="inlineStr">
+        <is>
+          <t>615.39</t>
+        </is>
+      </c>
+      <c r="C84" s="4" t="inlineStr">
+        <is>
+          <t>358.170.962-77</t>
+        </is>
+      </c>
+      <c r="D84" s="4" t="inlineStr">
+        <is>
+          <t>13/07/2024</t>
+        </is>
+      </c>
+      <c r="E84" s="4" t="inlineStr">
+        <is>
+          <t>Pago</t>
+        </is>
+      </c>
+      <c r="F84" s="4" t="inlineStr">
+        <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="G84" s="4" t="inlineStr">
+        <is>
+          <t>CARTÃO</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="4" t="inlineStr">
+        <is>
+          <t>Dra. Alícia Monteiro</t>
+        </is>
+      </c>
+      <c r="B85" s="4" t="inlineStr">
+        <is>
+          <t>726.43</t>
+        </is>
+      </c>
+      <c r="C85" s="4" t="inlineStr">
+        <is>
+          <t>098.132.475-41</t>
+        </is>
+      </c>
+      <c r="D85" s="4" t="inlineStr">
+        <is>
+          <t>26/06/2024</t>
+        </is>
+      </c>
+      <c r="E85" s="4" t="inlineStr">
+        <is>
+          <t>Pago</t>
+        </is>
+      </c>
+      <c r="F85" s="4" t="inlineStr">
+        <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="G85" s="4" t="inlineStr">
+        <is>
+          <t>CARTÃO</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="4" t="inlineStr">
+        <is>
+          <t>Eduardo Farias</t>
+        </is>
+      </c>
+      <c r="B86" s="4" t="inlineStr">
+        <is>
+          <t>370.38</t>
+        </is>
+      </c>
+      <c r="C86" s="4" t="inlineStr">
+        <is>
+          <t>203.546.178-26</t>
+        </is>
+      </c>
+      <c r="D86" s="4" t="inlineStr">
+        <is>
+          <t>23/06/2024</t>
+        </is>
+      </c>
+      <c r="E86" s="4" t="inlineStr">
+        <is>
+          <t>Pago</t>
+        </is>
+      </c>
+      <c r="F86" s="4" t="inlineStr">
+        <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="G86" s="4" t="inlineStr">
+        <is>
+          <t>CARTÃO</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="4" t="inlineStr">
+        <is>
+          <t>Dr. Gustavo Costa</t>
+        </is>
+      </c>
+      <c r="B87" s="4" t="inlineStr">
+        <is>
+          <t>949.45</t>
+        </is>
+      </c>
+      <c r="C87" s="4" t="inlineStr">
+        <is>
+          <t>916.253.408-42</t>
+        </is>
+      </c>
+      <c r="D87" s="4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E87" s="4" t="inlineStr">
+        <is>
+          <t>Erro ao coletar</t>
+        </is>
+      </c>
+      <c r="F87" s="4" t="inlineStr">
+        <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="G87" s="4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="4" t="inlineStr">
+        <is>
+          <t>Noah da Mota</t>
+        </is>
+      </c>
+      <c r="B88" s="4" t="inlineStr">
+        <is>
+          <t>747.91</t>
+        </is>
+      </c>
+      <c r="C88" s="4" t="inlineStr">
+        <is>
+          <t>472.963.815-82</t>
+        </is>
+      </c>
+      <c r="D88" s="4" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="E88" s="4" t="inlineStr">
+        <is>
+          <t>Cadastrado</t>
+        </is>
+      </c>
+      <c r="F88" s="4" t="inlineStr">
+        <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="G88" s="4" t="inlineStr">
+        <is>
+          <t>cartao_credito</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="4" t="inlineStr">
+        <is>
+          <t>Carlos Eduardo Santos</t>
+        </is>
+      </c>
+      <c r="B89" s="4" t="inlineStr">
+        <is>
+          <t>123.2</t>
+        </is>
+      </c>
+      <c r="C89" s="4" t="inlineStr">
+        <is>
+          <t>231.659.708-40</t>
+        </is>
+      </c>
+      <c r="D89" s="4" t="inlineStr">
+        <is>
+          <t>07/12/2025</t>
+        </is>
+      </c>
+      <c r="E89" s="4" t="inlineStr">
+        <is>
+          <t>Cadastrado</t>
+        </is>
+      </c>
+      <c r="F89" s="4" t="inlineStr">
+        <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="G89" s="4" t="inlineStr">
+        <is>
+          <t>cartao_credito</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="4" t="inlineStr">
+        <is>
+          <t>Noah da Mota</t>
+        </is>
+      </c>
+      <c r="B90" s="4" t="inlineStr">
+        <is>
+          <t>747.91</t>
+        </is>
+      </c>
+      <c r="C90" s="4" t="inlineStr">
+        <is>
+          <t>472.963.815-82</t>
+        </is>
+      </c>
+      <c r="D90" s="4" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="E90" s="4" t="inlineStr">
+        <is>
+          <t>Cadastrado</t>
+        </is>
+      </c>
+      <c r="F90" s="4" t="inlineStr">
+        <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="G90" s="4" t="inlineStr">
+        <is>
+          <t>cartao_credito</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="4" t="inlineStr">
+        <is>
+          <t>Carlos Eduardo Santos</t>
+        </is>
+      </c>
+      <c r="B91" s="4" t="inlineStr">
+        <is>
+          <t>123.2</t>
+        </is>
+      </c>
+      <c r="C91" s="4" t="inlineStr">
+        <is>
+          <t>231.659.708-40</t>
+        </is>
+      </c>
+      <c r="D91" s="4" t="inlineStr">
+        <is>
+          <t>07/12/2025</t>
+        </is>
+      </c>
+      <c r="E91" s="4" t="inlineStr">
+        <is>
+          <t>Cadastrado</t>
+        </is>
+      </c>
+      <c r="F91" s="4" t="inlineStr">
+        <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="G91" s="4" t="inlineStr">
+        <is>
+          <t>cartao_credito</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="4" t="inlineStr">
+        <is>
+          <t>Noah da Mota</t>
+        </is>
+      </c>
+      <c r="B92" s="4" t="inlineStr">
+        <is>
+          <t>747.91</t>
+        </is>
+      </c>
+      <c r="C92" s="4" t="inlineStr">
+        <is>
+          <t>472.963.815-82</t>
+        </is>
+      </c>
+      <c r="D92" s="4" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="E92" s="4" t="inlineStr">
+        <is>
+          <t>Cadastrado</t>
+        </is>
+      </c>
+      <c r="F92" s="4" t="inlineStr">
+        <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="G92" s="4" t="inlineStr">
+        <is>
+          <t>cartao_credito</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="4" t="inlineStr">
+        <is>
+          <t>Carlos Eduardo Santos</t>
+        </is>
+      </c>
+      <c r="B93" s="4" t="inlineStr">
+        <is>
+          <t>123.2</t>
+        </is>
+      </c>
+      <c r="C93" s="4" t="inlineStr">
+        <is>
+          <t>231.659.708-40</t>
+        </is>
+      </c>
+      <c r="D93" s="4" t="inlineStr">
+        <is>
+          <t>07/12/2025</t>
+        </is>
+      </c>
+      <c r="E93" s="4" t="inlineStr">
+        <is>
+          <t>Cadastrado</t>
+        </is>
+      </c>
+      <c r="F93" s="4" t="inlineStr">
+        <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="G93" s="4" t="inlineStr">
+        <is>
+          <t>cartao_credito</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="4" t="inlineStr">
+        <is>
+          <t>Dr. Felipe Farias</t>
+        </is>
+      </c>
+      <c r="B94" s="4" t="inlineStr">
+        <is>
+          <t>285.56</t>
+        </is>
+      </c>
+      <c r="C94" s="4" t="inlineStr">
+        <is>
+          <t>487.039.126-04</t>
+        </is>
+      </c>
+      <c r="D94" s="4" t="inlineStr">
+        <is>
+          <t>07/02/2026</t>
+        </is>
+      </c>
+      <c r="E94" s="4" t="inlineStr">
+        <is>
+          <t>Cadastrado</t>
+        </is>
+      </c>
+      <c r="F94" s="4" t="inlineStr">
+        <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="G94" s="4" t="inlineStr">
+        <is>
+          <t>cartao_credito</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="4" t="inlineStr">
+        <is>
+          <t>Luigi Barros</t>
+        </is>
+      </c>
+      <c r="B95" s="4" t="inlineStr">
+        <is>
+          <t>349.87</t>
+        </is>
+      </c>
+      <c r="C95" s="4" t="inlineStr">
+        <is>
+          <t>179.432.680-40</t>
+        </is>
+      </c>
+      <c r="D95" s="4" t="inlineStr">
+        <is>
+          <t>29/06/2025</t>
+        </is>
+      </c>
+      <c r="E95" s="4" t="inlineStr">
+        <is>
+          <t>Cadastrado</t>
+        </is>
+      </c>
+      <c r="F95" s="4" t="inlineStr">
+        <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="G95" s="4" t="inlineStr">
+        <is>
+          <t>cartao_credito</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="4" t="inlineStr">
+        <is>
+          <t>Stella da Luz</t>
+        </is>
+      </c>
+      <c r="B96" s="4" t="inlineStr">
+        <is>
+          <t>449.42</t>
+        </is>
+      </c>
+      <c r="C96" s="4" t="inlineStr">
+        <is>
+          <t>821.074.653-71</t>
+        </is>
+      </c>
+      <c r="D96" s="4" t="inlineStr">
+        <is>
+          <t>16/07/2024</t>
+        </is>
+      </c>
+      <c r="E96" s="4" t="inlineStr">
+        <is>
+          <t>Cadastrado</t>
+        </is>
+      </c>
+      <c r="F96" s="4" t="inlineStr">
+        <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="G96" s="4" t="inlineStr">
+        <is>
+          <t>cartao_credito</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="4" t="inlineStr">
+        <is>
+          <t>Elisa da Cunha</t>
+        </is>
+      </c>
+      <c r="B97" s="4" t="inlineStr">
+        <is>
+          <t>655.34</t>
+        </is>
+      </c>
+      <c r="C97" s="4" t="inlineStr">
+        <is>
+          <t>281.597.640-49</t>
+        </is>
+      </c>
+      <c r="D97" s="4" t="inlineStr">
+        <is>
+          <t>07/05/2024</t>
+        </is>
+      </c>
+      <c r="E97" s="4" t="inlineStr">
+        <is>
+          <t>Cadastrado</t>
+        </is>
+      </c>
+      <c r="F97" s="4" t="inlineStr">
+        <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="G97" s="4" t="inlineStr">
+        <is>
+          <t>cartao_credito</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="4" t="inlineStr">
+        <is>
+          <t>Rodrigo Fernandes</t>
+        </is>
+      </c>
+      <c r="B98" s="4" t="inlineStr">
+        <is>
+          <t>615.39</t>
+        </is>
+      </c>
+      <c r="C98" s="4" t="inlineStr">
+        <is>
+          <t>358.170.962-77</t>
+        </is>
+      </c>
+      <c r="D98" s="4" t="inlineStr">
+        <is>
+          <t>13/07/2024</t>
+        </is>
+      </c>
+      <c r="E98" s="4" t="inlineStr">
+        <is>
+          <t>Cadastrado</t>
+        </is>
+      </c>
+      <c r="F98" s="4" t="inlineStr">
+        <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="G98" s="4" t="inlineStr">
+        <is>
+          <t>cartao_credito</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="4" t="inlineStr">
+        <is>
+          <t>Noah da Mota</t>
+        </is>
+      </c>
+      <c r="B99" s="4" t="inlineStr">
+        <is>
+          <t>747.91</t>
+        </is>
+      </c>
+      <c r="C99" s="4" t="inlineStr">
+        <is>
+          <t>472.963.815-82</t>
+        </is>
+      </c>
+      <c r="D99" s="4" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="E99" s="4" t="inlineStr">
+        <is>
+          <t>Pago</t>
+        </is>
+      </c>
+      <c r="F99" s="4" t="inlineStr">
+        <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="G99" s="4" t="inlineStr">
+        <is>
+          <t>CARTÃO CRÉDITO</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="4" t="inlineStr">
+        <is>
+          <t>Carlos Eduardo Santos</t>
+        </is>
+      </c>
+      <c r="B100" s="4" t="inlineStr">
+        <is>
+          <t>123.2</t>
+        </is>
+      </c>
+      <c r="C100" s="4" t="inlineStr">
+        <is>
+          <t>231.659.708-40</t>
+        </is>
+      </c>
+      <c r="D100" s="4" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="E100" s="4" t="inlineStr">
+        <is>
+          <t>Pago</t>
+        </is>
+      </c>
+      <c r="F100" s="4" t="inlineStr">
+        <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="G100" s="4" t="inlineStr">
+        <is>
+          <t>CARTÃO CRÉDITO</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="4" t="inlineStr">
+        <is>
+          <t>Dr. Felipe Farias</t>
+        </is>
+      </c>
+      <c r="B101" s="4" t="inlineStr">
+        <is>
+          <t>285.56</t>
+        </is>
+      </c>
+      <c r="C101" s="4" t="inlineStr">
+        <is>
+          <t>487.039.126-04</t>
+        </is>
+      </c>
+      <c r="D101" s="4" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="E101" s="4" t="inlineStr">
+        <is>
+          <t>Pago</t>
+        </is>
+      </c>
+      <c r="F101" s="4" t="inlineStr">
+        <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="G101" s="4" t="inlineStr">
+        <is>
+          <t>CARTÃO CRÉDITO</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="4" t="inlineStr">
+        <is>
+          <t>Luigi Barros</t>
+        </is>
+      </c>
+      <c r="B102" s="4" t="inlineStr">
+        <is>
+          <t>349.87</t>
+        </is>
+      </c>
+      <c r="C102" s="4" t="inlineStr">
+        <is>
+          <t>179.432.680-40</t>
+        </is>
+      </c>
+      <c r="D102" s="4" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="E102" s="4" t="inlineStr">
+        <is>
+          <t>Pago</t>
+        </is>
+      </c>
+      <c r="F102" s="4" t="inlineStr">
+        <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="G102" s="4" t="inlineStr">
+        <is>
+          <t>CARTÃO CRÉDITO</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="4" t="inlineStr">
+        <is>
+          <t>Stella da Luz</t>
+        </is>
+      </c>
+      <c r="B103" s="4" t="inlineStr">
+        <is>
+          <t>449.42</t>
+        </is>
+      </c>
+      <c r="C103" s="4" t="inlineStr">
+        <is>
+          <t>821.074.653-71</t>
+        </is>
+      </c>
+      <c r="D103" s="4" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="E103" s="4" t="inlineStr">
+        <is>
+          <t>Pago</t>
+        </is>
+      </c>
+      <c r="F103" s="4" t="inlineStr">
+        <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="G103" s="4" t="inlineStr">
+        <is>
+          <t>CARTÃO CRÉDITO</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="4" t="inlineStr">
+        <is>
+          <t>Elisa da Cunha</t>
+        </is>
+      </c>
+      <c r="B104" s="4" t="inlineStr">
+        <is>
+          <t>655.34</t>
+        </is>
+      </c>
+      <c r="C104" s="4" t="inlineStr">
+        <is>
+          <t>281.597.640-49</t>
+        </is>
+      </c>
+      <c r="D104" s="4" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="E104" s="4" t="inlineStr">
+        <is>
+          <t>Pago</t>
+        </is>
+      </c>
+      <c r="F104" s="4" t="inlineStr">
+        <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="G104" s="4" t="inlineStr">
+        <is>
+          <t>CARTÃO CRÉDITO</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="4" t="inlineStr">
+        <is>
+          <t>Rodrigo Fernandes</t>
+        </is>
+      </c>
+      <c r="B105" s="4" t="inlineStr">
+        <is>
+          <t>615.39</t>
+        </is>
+      </c>
+      <c r="C105" s="4" t="inlineStr">
+        <is>
+          <t>358.170.962-77</t>
+        </is>
+      </c>
+      <c r="D105" s="4" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="E105" s="4" t="inlineStr">
+        <is>
+          <t>Pago</t>
+        </is>
+      </c>
+      <c r="F105" s="4" t="inlineStr">
+        <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="G105" s="4" t="inlineStr">
+        <is>
+          <t>CARTÃO CRÉDITO</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="4" t="inlineStr">
+        <is>
+          <t>Dra. Alícia Monteiro</t>
+        </is>
+      </c>
+      <c r="B106" s="4" t="inlineStr">
+        <is>
+          <t>726.43</t>
+        </is>
+      </c>
+      <c r="C106" s="4" t="inlineStr">
+        <is>
+          <t>098.132.475-41</t>
+        </is>
+      </c>
+      <c r="D106" s="4" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="E106" s="4" t="inlineStr">
+        <is>
+          <t>Pago</t>
+        </is>
+      </c>
+      <c r="F106" s="4" t="inlineStr">
+        <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="G106" s="4" t="inlineStr">
+        <is>
+          <t>CARTÃO CRÉDITO</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="4" t="inlineStr">
+        <is>
+          <t>Eduardo Farias</t>
+        </is>
+      </c>
+      <c r="B107" s="4" t="inlineStr">
+        <is>
+          <t>370.38</t>
+        </is>
+      </c>
+      <c r="C107" s="4" t="inlineStr">
+        <is>
+          <t>203.546.178-26</t>
+        </is>
+      </c>
+      <c r="D107" s="4" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="E107" s="4" t="inlineStr">
+        <is>
+          <t>Pago</t>
+        </is>
+      </c>
+      <c r="F107" s="4" t="inlineStr">
+        <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="G107" s="4" t="inlineStr">
+        <is>
+          <t>CARTÃO CRÉDITO</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="4" t="inlineStr">
+        <is>
+          <t>Dr. Gustavo Costa</t>
+        </is>
+      </c>
+      <c r="B108" s="4" t="inlineStr">
+        <is>
+          <t>949.45</t>
+        </is>
+      </c>
+      <c r="C108" s="4" t="inlineStr">
+        <is>
+          <t>916.253.408-42</t>
+        </is>
+      </c>
+      <c r="D108" s="4" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="E108" s="4" t="inlineStr">
+        <is>
+          <t>Pago</t>
+        </is>
+      </c>
+      <c r="F108" s="4" t="inlineStr">
+        <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="G108" s="4" t="inlineStr">
+        <is>
+          <t>CARTÃO CRÉDITO</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="4" t="inlineStr">
+        <is>
+          <t>Sarah Fogaça</t>
+        </is>
+      </c>
+      <c r="B109" s="4" t="inlineStr">
+        <is>
+          <t>661.26</t>
+        </is>
+      </c>
+      <c r="C109" s="4" t="inlineStr">
+        <is>
+          <t>197.382.460-40</t>
+        </is>
+      </c>
+      <c r="D109" s="4" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="E109" s="4" t="inlineStr">
+        <is>
+          <t>Pago</t>
+        </is>
+      </c>
+      <c r="F109" s="4" t="inlineStr">
+        <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="G109" s="4" t="inlineStr">
+        <is>
+          <t>CARTÃO CRÉDITO</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="4" t="inlineStr">
+        <is>
+          <t>Thomas Costa</t>
+        </is>
+      </c>
+      <c r="B110" s="4" t="inlineStr">
+        <is>
+          <t>375.81</t>
+        </is>
+      </c>
+      <c r="C110" s="4" t="inlineStr">
+        <is>
+          <t>732.481.056-07</t>
+        </is>
+      </c>
+      <c r="D110" s="4" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="E110" s="4" t="inlineStr">
+        <is>
+          <t>Pago</t>
+        </is>
+      </c>
+      <c r="F110" s="4" t="inlineStr">
+        <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="G110" s="4" t="inlineStr">
+        <is>
+          <t>CARTÃO CRÉDITO</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="4" t="inlineStr">
+        <is>
+          <t>João Felipe Aragão</t>
+        </is>
+      </c>
+      <c r="B111" s="4" t="inlineStr">
+        <is>
+          <t>666.93</t>
+        </is>
+      </c>
+      <c r="C111" s="4" t="inlineStr">
+        <is>
+          <t>839.140.256-89</t>
+        </is>
+      </c>
+      <c r="D111" s="4" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="E111" s="4" t="inlineStr">
+        <is>
+          <t>Pago</t>
+        </is>
+      </c>
+      <c r="F111" s="4" t="inlineStr">
+        <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="G111" s="4" t="inlineStr">
+        <is>
+          <t>CARTÃO CRÉDITO</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="4" t="inlineStr">
+        <is>
+          <t>Dra. Nina Caldeira</t>
+        </is>
+      </c>
+      <c r="B112" s="4" t="inlineStr">
+        <is>
+          <t>618.96</t>
+        </is>
+      </c>
+      <c r="C112" s="4" t="inlineStr">
+        <is>
+          <t>903.158.764-84</t>
+        </is>
+      </c>
+      <c r="D112" s="4" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="E112" s="4" t="inlineStr">
+        <is>
+          <t>Pago</t>
+        </is>
+      </c>
+      <c r="F112" s="4" t="inlineStr">
+        <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="G112" s="4" t="inlineStr">
+        <is>
+          <t>CARTÃO CRÉDITO</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="4" t="inlineStr">
+        <is>
+          <t>Pietra Correia</t>
+        </is>
+      </c>
+      <c r="B113" s="4" t="inlineStr">
+        <is>
+          <t>737.74</t>
+        </is>
+      </c>
+      <c r="C113" s="4" t="inlineStr">
+        <is>
+          <t>392.104.568-15</t>
+        </is>
+      </c>
+      <c r="D113" s="4" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="E113" s="4" t="inlineStr">
+        <is>
+          <t>Pago</t>
+        </is>
+      </c>
+      <c r="F113" s="4" t="inlineStr">
+        <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="G113" s="4" t="inlineStr">
+        <is>
+          <t>CARTÃO CRÉDITO</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="4" t="inlineStr">
+        <is>
+          <t>Enzo Gabriel Lima</t>
+        </is>
+      </c>
+      <c r="B114" s="4" t="inlineStr">
+        <is>
+          <t>791.46</t>
+        </is>
+      </c>
+      <c r="C114" s="4" t="inlineStr">
+        <is>
+          <t>185.603.294-98</t>
+        </is>
+      </c>
+      <c r="D114" s="4" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="E114" s="4" t="inlineStr">
+        <is>
+          <t>Pago</t>
+        </is>
+      </c>
+      <c r="F114" s="4" t="inlineStr">
+        <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="G114" s="4" t="inlineStr">
+        <is>
+          <t>CARTÃO CRÉDITO</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="4" t="inlineStr">
+        <is>
+          <t>Bianca Azevedo</t>
+        </is>
+      </c>
+      <c r="B115" s="4" t="inlineStr">
+        <is>
+          <t>852.28</t>
+        </is>
+      </c>
+      <c r="C115" s="4" t="inlineStr">
+        <is>
+          <t>143.789.560-39</t>
+        </is>
+      </c>
+      <c r="D115" s="4" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="E115" s="4" t="inlineStr">
+        <is>
+          <t>Pago</t>
+        </is>
+      </c>
+      <c r="F115" s="4" t="inlineStr">
+        <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="G115" s="4" t="inlineStr">
+        <is>
+          <t>CARTÃO CRÉDITO</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="4" t="inlineStr">
+        <is>
+          <t>Fernanda Martins</t>
+        </is>
+      </c>
+      <c r="B116" s="4" t="inlineStr">
+        <is>
+          <t>523.92</t>
+        </is>
+      </c>
+      <c r="C116" s="4" t="inlineStr">
+        <is>
+          <t>852.436.970-10</t>
+        </is>
+      </c>
+      <c r="D116" s="4" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="E116" s="4" t="inlineStr">
+        <is>
+          <t>Pago</t>
+        </is>
+      </c>
+      <c r="F116" s="4" t="inlineStr">
+        <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="G116" s="4" t="inlineStr">
+        <is>
+          <t>CARTÃO CRÉDITO</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="4" t="inlineStr">
+        <is>
+          <t>Eduardo Novaes</t>
+        </is>
+      </c>
+      <c r="B117" s="4" t="inlineStr">
+        <is>
+          <t>453.74</t>
+        </is>
+      </c>
+      <c r="C117" s="4" t="inlineStr">
+        <is>
+          <t>382.567.490-83</t>
+        </is>
+      </c>
+      <c r="D117" s="4" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="E117" s="4" t="inlineStr">
+        <is>
+          <t>Pago</t>
+        </is>
+      </c>
+      <c r="F117" s="4" t="inlineStr">
+        <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="G117" s="4" t="inlineStr">
+        <is>
+          <t>CARTÃO CRÉDITO</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="4" t="inlineStr">
+        <is>
+          <t>Luiz Miguel Rodrigues</t>
+        </is>
+      </c>
+      <c r="B118" s="4" t="inlineStr">
+        <is>
+          <t>278.83</t>
+        </is>
+      </c>
+      <c r="C118" s="4" t="inlineStr">
+        <is>
+          <t>903.468.752-00</t>
+        </is>
+      </c>
+      <c r="D118" s="4" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="E118" s="4" t="inlineStr">
+        <is>
+          <t>Pago</t>
+        </is>
+      </c>
+      <c r="F118" s="4" t="inlineStr">
+        <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="G118" s="4" t="inlineStr">
+        <is>
+          <t>CARTÃO CRÉDITO</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="4" t="inlineStr">
+        <is>
+          <t>Alexandre Ramos</t>
+        </is>
+      </c>
+      <c r="B119" s="4" t="inlineStr">
+        <is>
+          <t>495.02</t>
+        </is>
+      </c>
+      <c r="C119" s="4" t="inlineStr">
+        <is>
+          <t>370.549.268-38</t>
+        </is>
+      </c>
+      <c r="D119" s="4" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="E119" s="4" t="inlineStr">
+        <is>
+          <t>Pago</t>
+        </is>
+      </c>
+      <c r="F119" s="4" t="inlineStr">
+        <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="G119" s="4" t="inlineStr">
+        <is>
+          <t>CARTÃO CRÉDITO</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="4" t="inlineStr">
+        <is>
+          <t>Danilo Peixoto</t>
+        </is>
+      </c>
+      <c r="B120" s="4" t="inlineStr">
+        <is>
+          <t>527.24</t>
+        </is>
+      </c>
+      <c r="C120" s="4" t="inlineStr">
+        <is>
+          <t>379.681.520-03</t>
+        </is>
+      </c>
+      <c r="D120" s="4" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="E120" s="4" t="inlineStr">
+        <is>
+          <t>Pago</t>
+        </is>
+      </c>
+      <c r="F120" s="4" t="inlineStr">
+        <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="G120" s="4" t="inlineStr">
+        <is>
+          <t>CARTÃO CRÉDITO</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="4" t="inlineStr">
+        <is>
+          <t>Maria Eduarda Barbosa</t>
+        </is>
+      </c>
+      <c r="B121" s="4" t="inlineStr">
+        <is>
+          <t>164.61</t>
+        </is>
+      </c>
+      <c r="C121" s="4" t="inlineStr">
+        <is>
+          <t>068.719.435-01</t>
+        </is>
+      </c>
+      <c r="D121" s="4" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="E121" s="4" t="inlineStr">
+        <is>
+          <t>Pago</t>
+        </is>
+      </c>
+      <c r="F121" s="4" t="inlineStr">
+        <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="G121" s="4" t="inlineStr">
+        <is>
+          <t>CARTÃO CRÉDITO</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="4" t="inlineStr">
+        <is>
+          <t>Luiza Teixeira</t>
+        </is>
+      </c>
+      <c r="B122" s="4" t="inlineStr">
+        <is>
+          <t>236.86</t>
+        </is>
+      </c>
+      <c r="C122" s="4" t="inlineStr">
+        <is>
+          <t>394.275.610-25</t>
+        </is>
+      </c>
+      <c r="D122" s="4" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="E122" s="4" t="inlineStr">
+        <is>
+          <t>Pago</t>
+        </is>
+      </c>
+      <c r="F122" s="4" t="inlineStr">
+        <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="G122" s="4" t="inlineStr">
+        <is>
+          <t>CARTÃO CRÉDITO</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="4" t="inlineStr">
+        <is>
+          <t>Sr. Gabriel Ramos</t>
+        </is>
+      </c>
+      <c r="B123" s="4" t="inlineStr">
+        <is>
+          <t>942.09</t>
+        </is>
+      </c>
+      <c r="C123" s="4" t="inlineStr">
+        <is>
+          <t>467.831.950-66</t>
+        </is>
+      </c>
+      <c r="D123" s="4" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="E123" s="4" t="inlineStr">
+        <is>
+          <t>Pago</t>
+        </is>
+      </c>
+      <c r="F123" s="4" t="inlineStr">
+        <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="G123" s="4" t="inlineStr">
+        <is>
+          <t>CARTÃO CRÉDITO</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="4" t="inlineStr">
+        <is>
+          <t>Theo Oliveira</t>
+        </is>
+      </c>
+      <c r="B124" s="4" t="inlineStr">
+        <is>
+          <t>858.2</t>
+        </is>
+      </c>
+      <c r="C124" s="4" t="inlineStr">
+        <is>
+          <t>407.856.913-75</t>
+        </is>
+      </c>
+      <c r="D124" s="4" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="E124" s="4" t="inlineStr">
+        <is>
+          <t>Pago</t>
+        </is>
+      </c>
+      <c r="F124" s="4" t="inlineStr">
+        <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="G124" s="4" t="inlineStr">
+        <is>
+          <t>CARTÃO CRÉDITO</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="4" t="inlineStr">
+        <is>
+          <t>Levi Caldeira</t>
+        </is>
+      </c>
+      <c r="B125" s="4" t="inlineStr">
+        <is>
+          <t>913.08</t>
+        </is>
+      </c>
+      <c r="C125" s="4" t="inlineStr">
+        <is>
+          <t>427.839.561-28</t>
+        </is>
+      </c>
+      <c r="D125" s="4" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="E125" s="4" t="inlineStr">
+        <is>
+          <t>Pago</t>
+        </is>
+      </c>
+      <c r="F125" s="4" t="inlineStr">
+        <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="G125" s="4" t="inlineStr">
+        <is>
+          <t>CARTÃO CRÉDITO</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="4" t="inlineStr">
+        <is>
+          <t>Sr. Francisco Moura</t>
+        </is>
+      </c>
+      <c r="B126" s="4" t="inlineStr">
+        <is>
+          <t>294.91</t>
+        </is>
+      </c>
+      <c r="C126" s="4" t="inlineStr">
+        <is>
+          <t>912.045.687-58</t>
+        </is>
+      </c>
+      <c r="D126" s="4" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="E126" s="4" t="inlineStr">
+        <is>
+          <t>Pago</t>
+        </is>
+      </c>
+      <c r="F126" s="4" t="inlineStr">
+        <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="G126" s="4" t="inlineStr">
+        <is>
+          <t>CARTÃO CRÉDITO</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="4" t="inlineStr">
+        <is>
+          <t>Miguel Carvalho</t>
+        </is>
+      </c>
+      <c r="B127" s="4" t="inlineStr">
+        <is>
+          <t>118.37</t>
+        </is>
+      </c>
+      <c r="C127" s="4" t="inlineStr">
+        <is>
+          <t>497.102.653-34</t>
+        </is>
+      </c>
+      <c r="D127" s="4" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="E127" s="4" t="inlineStr">
+        <is>
+          <t>Pago</t>
+        </is>
+      </c>
+      <c r="F127" s="4" t="inlineStr">
+        <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="G127" s="4" t="inlineStr">
+        <is>
+          <t>CARTÃO CRÉDITO</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="4" t="inlineStr">
+        <is>
+          <t>Lorena Gomes</t>
+        </is>
+      </c>
+      <c r="B128" s="4" t="inlineStr">
+        <is>
+          <t>492.57</t>
+        </is>
+      </c>
+      <c r="C128" s="4" t="inlineStr">
+        <is>
+          <t>324.071.596-16</t>
+        </is>
+      </c>
+      <c r="D128" s="4" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="E128" s="4" t="inlineStr">
+        <is>
+          <t>Pago</t>
+        </is>
+      </c>
+      <c r="F128" s="4" t="inlineStr">
+        <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="G128" s="4" t="inlineStr">
+        <is>
+          <t>CARTÃO CRÉDITO</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="4" t="inlineStr">
+        <is>
+          <t>Vitória Aragão</t>
+        </is>
+      </c>
+      <c r="B129" s="4" t="inlineStr">
+        <is>
+          <t>797.44</t>
+        </is>
+      </c>
+      <c r="C129" s="4" t="inlineStr">
+        <is>
+          <t>146.723.805-80</t>
+        </is>
+      </c>
+      <c r="D129" s="4" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="E129" s="4" t="inlineStr">
+        <is>
+          <t>Pago</t>
+        </is>
+      </c>
+      <c r="F129" s="4" t="inlineStr">
+        <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="G129" s="4" t="inlineStr">
+        <is>
+          <t>CARTÃO CRÉDITO</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="4" t="inlineStr">
+        <is>
+          <t>João Guilherme Costela</t>
+        </is>
+      </c>
+      <c r="B130" s="4" t="inlineStr">
+        <is>
+          <t>247.62</t>
+        </is>
+      </c>
+      <c r="C130" s="4" t="inlineStr">
+        <is>
+          <t>865.493.107-84</t>
+        </is>
+      </c>
+      <c r="D130" s="4" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="E130" s="4" t="inlineStr">
+        <is>
+          <t>Pago</t>
+        </is>
+      </c>
+      <c r="F130" s="4" t="inlineStr">
+        <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="G130" s="4" t="inlineStr">
+        <is>
+          <t>CARTÃO CRÉDITO</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="4" t="inlineStr">
+        <is>
+          <t>Guilherme da Rocha</t>
+        </is>
+      </c>
+      <c r="B131" s="4" t="inlineStr">
+        <is>
+          <t>675.64</t>
+        </is>
+      </c>
+      <c r="C131" s="4" t="inlineStr">
+        <is>
+          <t>921.057.386-21</t>
+        </is>
+      </c>
+      <c r="D131" s="4" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="E131" s="4" t="inlineStr">
+        <is>
+          <t>Pago</t>
+        </is>
+      </c>
+      <c r="F131" s="4" t="inlineStr">
+        <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="G131" s="4" t="inlineStr">
+        <is>
+          <t>CARTÃO CRÉDITO</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="4" t="inlineStr">
+        <is>
+          <t>Raquel Nascimento</t>
+        </is>
+      </c>
+      <c r="B132" s="4" t="inlineStr">
+        <is>
+          <t>978.63</t>
+        </is>
+      </c>
+      <c r="C132" s="4" t="inlineStr">
+        <is>
+          <t>924.783.506-29</t>
+        </is>
+      </c>
+      <c r="D132" s="4" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="E132" s="4" t="inlineStr">
+        <is>
+          <t>Pago</t>
+        </is>
+      </c>
+      <c r="F132" s="4" t="inlineStr">
+        <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="G132" s="4" t="inlineStr">
+        <is>
+          <t>CARTÃO CRÉDITO</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="4" t="inlineStr">
+        <is>
+          <t>Mariana Carvalho</t>
+        </is>
+      </c>
+      <c r="B133" s="4" t="inlineStr">
+        <is>
+          <t>670.58</t>
+        </is>
+      </c>
+      <c r="C133" s="4" t="inlineStr">
+        <is>
+          <t>326.081.957-68</t>
+        </is>
+      </c>
+      <c r="D133" s="4" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="E133" s="4" t="inlineStr">
+        <is>
+          <t>Pago</t>
+        </is>
+      </c>
+      <c r="F133" s="4" t="inlineStr">
+        <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="G133" s="4" t="inlineStr">
+        <is>
+          <t>CARTÃO CRÉDITO</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="4" t="inlineStr">
+        <is>
+          <t>Laura Ramos</t>
+        </is>
+      </c>
+      <c r="B134" s="4" t="inlineStr">
+        <is>
+          <t>341.26</t>
+        </is>
+      </c>
+      <c r="C134" s="4" t="inlineStr">
+        <is>
+          <t>052.163.874-71</t>
+        </is>
+      </c>
+      <c r="D134" s="4" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="E134" s="4" t="inlineStr">
+        <is>
+          <t>Pago</t>
+        </is>
+      </c>
+      <c r="F134" s="4" t="inlineStr">
+        <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="G134" s="4" t="inlineStr">
+        <is>
+          <t>CARTÃO CRÉDITO</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="4" t="inlineStr">
+        <is>
+          <t>Davi da Cunha</t>
+        </is>
+      </c>
+      <c r="B135" s="4" t="inlineStr">
+        <is>
+          <t>510.08</t>
+        </is>
+      </c>
+      <c r="C135" s="4" t="inlineStr">
+        <is>
+          <t>425.068.197-11</t>
+        </is>
+      </c>
+      <c r="D135" s="4" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="E135" s="4" t="inlineStr">
+        <is>
+          <t>Pago</t>
+        </is>
+      </c>
+      <c r="F135" s="4" t="inlineStr">
+        <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="G135" s="4" t="inlineStr">
+        <is>
+          <t>CARTÃO CRÉDITO</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="4" t="inlineStr">
+        <is>
+          <t>Ana Beatriz Sales</t>
+        </is>
+      </c>
+      <c r="B136" s="4" t="inlineStr">
+        <is>
+          <t>908.97</t>
+        </is>
+      </c>
+      <c r="C136" s="4" t="inlineStr">
+        <is>
+          <t>694.830.271-87</t>
+        </is>
+      </c>
+      <c r="D136" s="4" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="E136" s="4" t="inlineStr">
+        <is>
+          <t>Pago</t>
+        </is>
+      </c>
+      <c r="F136" s="4" t="inlineStr">
+        <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="G136" s="4" t="inlineStr">
+        <is>
+          <t>CARTÃO CRÉDITO</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="4" t="inlineStr">
+        <is>
+          <t>Melissa Silva</t>
+        </is>
+      </c>
+      <c r="B137" s="4" t="inlineStr">
+        <is>
+          <t>309.63</t>
+        </is>
+      </c>
+      <c r="C137" s="4" t="inlineStr">
+        <is>
+          <t>726.135.094-06</t>
+        </is>
+      </c>
+      <c r="D137" s="4" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="E137" s="4" t="inlineStr">
+        <is>
+          <t>Pago</t>
+        </is>
+      </c>
+      <c r="F137" s="4" t="inlineStr">
+        <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="G137" s="4" t="inlineStr">
+        <is>
+          <t>CARTÃO CRÉDITO</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="4" t="inlineStr">
+        <is>
+          <t>Vitor Hugo Duarte</t>
+        </is>
+      </c>
+      <c r="B138" s="4" t="inlineStr">
+        <is>
+          <t>808.59</t>
+        </is>
+      </c>
+      <c r="C138" s="4" t="inlineStr">
+        <is>
+          <t>543.712.986-64</t>
+        </is>
+      </c>
+      <c r="D138" s="4" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="E138" s="4" t="inlineStr">
+        <is>
+          <t>Pago</t>
+        </is>
+      </c>
+      <c r="F138" s="4" t="inlineStr">
+        <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="G138" s="4" t="inlineStr">
+        <is>
+          <t>CARTÃO CRÉDITO</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="4" t="inlineStr">
+        <is>
+          <t>Dr. Davi Fogaça</t>
+        </is>
+      </c>
+      <c r="B139" s="4" t="inlineStr">
+        <is>
+          <t>560.1</t>
+        </is>
+      </c>
+      <c r="C139" s="4" t="inlineStr">
+        <is>
+          <t>328.105.497-88</t>
+        </is>
+      </c>
+      <c r="D139" s="4" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="E139" s="4" t="inlineStr">
+        <is>
+          <t>Pago</t>
+        </is>
+      </c>
+      <c r="F139" s="4" t="inlineStr">
+        <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="G139" s="4" t="inlineStr">
+        <is>
+          <t>CARTÃO CRÉDITO</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="4" t="inlineStr">
+        <is>
+          <t>Marcela Moura</t>
+        </is>
+      </c>
+      <c r="B140" s="4" t="inlineStr">
+        <is>
+          <t>485.08</t>
+        </is>
+      </c>
+      <c r="C140" s="4" t="inlineStr">
+        <is>
+          <t>790.456.218-94</t>
+        </is>
+      </c>
+      <c r="D140" s="4" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="E140" s="4" t="inlineStr">
+        <is>
+          <t>Pago</t>
+        </is>
+      </c>
+      <c r="F140" s="4" t="inlineStr">
+        <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="G140" s="4" t="inlineStr">
+        <is>
+          <t>CARTÃO CRÉDITO</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="4" t="inlineStr">
+        <is>
+          <t>Nina Gomes</t>
+        </is>
+      </c>
+      <c r="B141" s="4" t="inlineStr">
+        <is>
+          <t>853.04</t>
+        </is>
+      </c>
+      <c r="C141" s="4" t="inlineStr">
+        <is>
+          <t>746.298.301-03</t>
+        </is>
+      </c>
+      <c r="D141" s="4" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="E141" s="4" t="inlineStr">
+        <is>
+          <t>Pago</t>
+        </is>
+      </c>
+      <c r="F141" s="4" t="inlineStr">
+        <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="G141" s="4" t="inlineStr">
+        <is>
+          <t>CARTÃO CRÉDITO</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="4" t="inlineStr">
+        <is>
+          <t>Maria Julia Dias</t>
+        </is>
+      </c>
+      <c r="B142" s="4" t="inlineStr">
+        <is>
+          <t>927.32</t>
+        </is>
+      </c>
+      <c r="C142" s="4" t="inlineStr">
+        <is>
+          <t>461.820.953-42</t>
+        </is>
+      </c>
+      <c r="D142" s="4" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="E142" s="4" t="inlineStr">
+        <is>
+          <t>Pago</t>
+        </is>
+      </c>
+      <c r="F142" s="4" t="inlineStr">
+        <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="G142" s="4" t="inlineStr">
+        <is>
+          <t>CARTÃO CRÉDITO</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="4" t="inlineStr">
+        <is>
+          <t>Danilo Duarte</t>
+        </is>
+      </c>
+      <c r="B143" s="4" t="inlineStr">
+        <is>
+          <t>836.33</t>
+        </is>
+      </c>
+      <c r="C143" s="4" t="inlineStr">
+        <is>
+          <t>930.126.874-40</t>
+        </is>
+      </c>
+      <c r="D143" s="4" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="E143" s="4" t="inlineStr">
+        <is>
+          <t>Pago</t>
+        </is>
+      </c>
+      <c r="F143" s="4" t="inlineStr">
+        <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="G143" s="4" t="inlineStr">
+        <is>
+          <t>CARTÃO CRÉDITO</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="4" t="inlineStr">
+        <is>
+          <t>Kevin Santos</t>
+        </is>
+      </c>
+      <c r="B144" s="4" t="inlineStr">
+        <is>
+          <t>469.74</t>
+        </is>
+      </c>
+      <c r="C144" s="4" t="inlineStr">
+        <is>
+          <t>107.483.259-05</t>
+        </is>
+      </c>
+      <c r="D144" s="4" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="E144" s="4" t="inlineStr">
+        <is>
+          <t>Pago</t>
+        </is>
+      </c>
+      <c r="F144" s="4" t="inlineStr">
+        <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="G144" s="4" t="inlineStr">
+        <is>
+          <t>CARTÃO CRÉDITO</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="4" t="inlineStr">
+        <is>
+          <t>Rebeca Moraes</t>
+        </is>
+      </c>
+      <c r="B145" s="4" t="inlineStr">
+        <is>
+          <t>185.48</t>
+        </is>
+      </c>
+      <c r="C145" s="4" t="inlineStr">
+        <is>
+          <t>496.321.057-61</t>
+        </is>
+      </c>
+      <c r="D145" s="4" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="E145" s="4" t="inlineStr">
+        <is>
+          <t>Pago</t>
+        </is>
+      </c>
+      <c r="F145" s="4" t="inlineStr">
+        <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="G145" s="4" t="inlineStr">
+        <is>
+          <t>CARTÃO CRÉDITO</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="4" t="inlineStr">
+        <is>
+          <t>Enzo Costela</t>
+        </is>
+      </c>
+      <c r="B146" s="4" t="inlineStr">
+        <is>
+          <t>807.96</t>
+        </is>
+      </c>
+      <c r="C146" s="4" t="inlineStr">
+        <is>
+          <t>835.742.961-00</t>
+        </is>
+      </c>
+      <c r="D146" s="4" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="E146" s="4" t="inlineStr">
+        <is>
+          <t>Pago</t>
+        </is>
+      </c>
+      <c r="F146" s="4" t="inlineStr">
+        <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="G146" s="4" t="inlineStr">
+        <is>
+          <t>CARTÃO CRÉDITO</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="4" t="inlineStr">
+        <is>
+          <t>Joaquim Viana</t>
+        </is>
+      </c>
+      <c r="B147" s="4" t="inlineStr">
+        <is>
+          <t>992.81</t>
+        </is>
+      </c>
+      <c r="C147" s="4" t="inlineStr">
+        <is>
+          <t>318.742.095-88</t>
+        </is>
+      </c>
+      <c r="D147" s="4" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="E147" s="4" t="inlineStr">
+        <is>
+          <t>Pago</t>
+        </is>
+      </c>
+      <c r="F147" s="4" t="inlineStr">
+        <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="G147" s="4" t="inlineStr">
+        <is>
+          <t>CARTÃO CRÉDITO</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="4" t="inlineStr">
+        <is>
+          <t>Isadora da Rosa</t>
+        </is>
+      </c>
+      <c r="B148" s="4" t="inlineStr">
+        <is>
+          <t>526.54</t>
+        </is>
+      </c>
+      <c r="C148" s="4" t="inlineStr">
+        <is>
+          <t>546.718.309-57</t>
+        </is>
+      </c>
+      <c r="D148" s="4" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="E148" s="4" t="inlineStr">
+        <is>
+          <t>Pago</t>
+        </is>
+      </c>
+      <c r="F148" s="4" t="inlineStr">
+        <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="G148" s="4" t="inlineStr">
+        <is>
+          <t>CARTÃO CRÉDITO</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="4" t="inlineStr">
+        <is>
+          <t>Yuri Freitas</t>
+        </is>
+      </c>
+      <c r="B149" s="4" t="inlineStr">
+        <is>
+          <t>725.75</t>
+        </is>
+      </c>
+      <c r="C149" s="4" t="inlineStr">
+        <is>
+          <t>047.298.165-01</t>
+        </is>
+      </c>
+      <c r="D149" s="4" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="E149" s="4" t="inlineStr">
+        <is>
+          <t>Pago</t>
+        </is>
+      </c>
+      <c r="F149" s="4" t="inlineStr">
+        <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="G149" s="4" t="inlineStr">
+        <is>
+          <t>CARTÃO CRÉDITO</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="4" t="inlineStr">
+        <is>
+          <t>Sabrina Pires</t>
+        </is>
+      </c>
+      <c r="B150" s="4" t="inlineStr">
+        <is>
+          <t>755.97</t>
+        </is>
+      </c>
+      <c r="C150" s="4" t="inlineStr">
+        <is>
+          <t>738.916.245-73</t>
+        </is>
+      </c>
+      <c r="D150" s="4" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="E150" s="4" t="inlineStr">
+        <is>
+          <t>Pago</t>
+        </is>
+      </c>
+      <c r="F150" s="4" t="inlineStr">
+        <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="G150" s="4" t="inlineStr">
+        <is>
+          <t>CARTÃO CRÉDITO</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="4" t="inlineStr">
+        <is>
+          <t>Julia Cunha</t>
+        </is>
+      </c>
+      <c r="B151" s="4" t="inlineStr">
+        <is>
+          <t>408.94</t>
+        </is>
+      </c>
+      <c r="C151" s="4" t="inlineStr">
+        <is>
+          <t>983.641.705-20</t>
+        </is>
+      </c>
+      <c r="D151" s="4" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="E151" s="4" t="inlineStr">
+        <is>
+          <t>Pago</t>
+        </is>
+      </c>
+      <c r="F151" s="4" t="inlineStr">
+        <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="G151" s="4" t="inlineStr">
+        <is>
+          <t>CARTÃO CRÉDITO</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="4" t="inlineStr">
+        <is>
+          <t>Dra. Maysa Souza</t>
+        </is>
+      </c>
+      <c r="B152" s="4" t="inlineStr">
+        <is>
+          <t>415.14</t>
+        </is>
+      </c>
+      <c r="C152" s="4" t="inlineStr">
+        <is>
+          <t>257.946.138-82</t>
+        </is>
+      </c>
+      <c r="D152" s="4" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="E152" s="4" t="inlineStr">
+        <is>
+          <t>Pago</t>
+        </is>
+      </c>
+      <c r="F152" s="4" t="inlineStr">
+        <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="G152" s="4" t="inlineStr">
+        <is>
+          <t>CARTÃO CRÉDITO</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="4" t="inlineStr">
+        <is>
+          <t>Stella da Paz</t>
+        </is>
+      </c>
+      <c r="B153" s="4" t="inlineStr">
+        <is>
+          <t>480.36</t>
+        </is>
+      </c>
+      <c r="C153" s="4" t="inlineStr">
+        <is>
+          <t>105.934.768-75</t>
+        </is>
+      </c>
+      <c r="D153" s="4" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="E153" s="4" t="inlineStr">
+        <is>
+          <t>Pago</t>
+        </is>
+      </c>
+      <c r="F153" s="4" t="inlineStr">
+        <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="G153" s="4" t="inlineStr">
+        <is>
+          <t>CARTÃO CRÉDITO</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="4" t="inlineStr">
+        <is>
+          <t>Dra. Bruna Rocha</t>
+        </is>
+      </c>
+      <c r="B154" s="4" t="inlineStr">
+        <is>
+          <t>763.34</t>
+        </is>
+      </c>
+      <c r="C154" s="4" t="inlineStr">
+        <is>
+          <t>910.645.237-06</t>
+        </is>
+      </c>
+      <c r="D154" s="4" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="E154" s="4" t="inlineStr">
+        <is>
+          <t>Pago</t>
+        </is>
+      </c>
+      <c r="F154" s="4" t="inlineStr">
+        <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="G154" s="4" t="inlineStr">
+        <is>
+          <t>CARTÃO CRÉDITO</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="4" t="inlineStr">
+        <is>
+          <t>Gustavo Silva</t>
+        </is>
+      </c>
+      <c r="B155" s="4" t="inlineStr">
+        <is>
+          <t>838.41</t>
+        </is>
+      </c>
+      <c r="C155" s="4" t="inlineStr">
+        <is>
+          <t>732.541.609-16</t>
+        </is>
+      </c>
+      <c r="D155" s="4" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="E155" s="4" t="inlineStr">
+        <is>
+          <t>Pago</t>
+        </is>
+      </c>
+      <c r="F155" s="4" t="inlineStr">
+        <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="G155" s="4" t="inlineStr">
+        <is>
+          <t>CARTÃO CRÉDITO</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="4" t="inlineStr">
+        <is>
+          <t>Isabella Moraes</t>
+        </is>
+      </c>
+      <c r="B156" s="4" t="inlineStr">
+        <is>
+          <t>105.66</t>
+        </is>
+      </c>
+      <c r="C156" s="4" t="inlineStr">
+        <is>
+          <t>236.981.475-64</t>
+        </is>
+      </c>
+      <c r="D156" s="4" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="E156" s="4" t="inlineStr">
+        <is>
+          <t>Pago</t>
+        </is>
+      </c>
+      <c r="F156" s="4" t="inlineStr">
+        <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="G156" s="4" t="inlineStr">
+        <is>
+          <t>CARTÃO CRÉDITO</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="4" t="inlineStr">
+        <is>
+          <t>Luiz Fernando Sales</t>
+        </is>
+      </c>
+      <c r="B157" s="4" t="inlineStr">
+        <is>
+          <t>820.29</t>
+        </is>
+      </c>
+      <c r="C157" s="4" t="inlineStr">
+        <is>
+          <t>867.504.291-49</t>
+        </is>
+      </c>
+      <c r="D157" s="4" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="E157" s="4" t="inlineStr">
+        <is>
+          <t>Pago</t>
+        </is>
+      </c>
+      <c r="F157" s="4" t="inlineStr">
+        <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="G157" s="4" t="inlineStr">
+        <is>
+          <t>CARTÃO CRÉDITO</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="4" t="inlineStr">
+        <is>
+          <t>Lavínia Costela</t>
+        </is>
+      </c>
+      <c r="B158" s="4" t="inlineStr">
+        <is>
+          <t>718.45</t>
+        </is>
+      </c>
+      <c r="C158" s="4" t="inlineStr">
+        <is>
+          <t>254.836.719-37</t>
+        </is>
+      </c>
+      <c r="D158" s="4" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="E158" s="4" t="inlineStr">
+        <is>
+          <t>Pago</t>
+        </is>
+      </c>
+      <c r="F158" s="4" t="inlineStr">
+        <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="G158" s="4" t="inlineStr">
+        <is>
+          <t>CARTÃO CRÉDITO</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="4" t="inlineStr">
+        <is>
+          <t>Dr. Juan Sales</t>
+        </is>
+      </c>
+      <c r="B159" s="4" t="inlineStr">
+        <is>
+          <t>301.55</t>
+        </is>
+      </c>
+      <c r="C159" s="4" t="inlineStr">
+        <is>
+          <t>463.710.892-69</t>
+        </is>
+      </c>
+      <c r="D159" s="4" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="E159" s="4" t="inlineStr">
+        <is>
+          <t>Pago</t>
+        </is>
+      </c>
+      <c r="F159" s="4" t="inlineStr">
+        <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="G159" s="4" t="inlineStr">
+        <is>
+          <t>CARTÃO CRÉDITO</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="4" t="inlineStr">
+        <is>
+          <t>Caio Mendes</t>
+        </is>
+      </c>
+      <c r="B160" s="4" t="inlineStr">
+        <is>
+          <t>572.25</t>
+        </is>
+      </c>
+      <c r="C160" s="4" t="inlineStr">
+        <is>
+          <t>152.480.763-07</t>
+        </is>
+      </c>
+      <c r="D160" s="4" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="E160" s="4" t="inlineStr">
+        <is>
+          <t>Pago</t>
+        </is>
+      </c>
+      <c r="F160" s="4" t="inlineStr">
+        <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="G160" s="4" t="inlineStr">
+        <is>
+          <t>CARTÃO CRÉDITO</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="4" t="inlineStr">
+        <is>
+          <t>Yuri Vieira</t>
+        </is>
+      </c>
+      <c r="B161" s="4" t="inlineStr">
+        <is>
+          <t>188.14</t>
+        </is>
+      </c>
+      <c r="C161" s="4" t="inlineStr">
+        <is>
+          <t>931.472.856-00</t>
+        </is>
+      </c>
+      <c r="D161" s="4" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="E161" s="4" t="inlineStr">
+        <is>
+          <t>Pago</t>
+        </is>
+      </c>
+      <c r="F161" s="4" t="inlineStr">
+        <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="G161" s="4" t="inlineStr">
+        <is>
+          <t>CARTÃO CRÉDITO</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="4" t="inlineStr">
+        <is>
+          <t>Vitor Gabriel Sales</t>
+        </is>
+      </c>
+      <c r="B162" s="4" t="inlineStr">
+        <is>
+          <t>253.4</t>
+        </is>
+      </c>
+      <c r="C162" s="4" t="inlineStr">
+        <is>
+          <t>132.096.475-34</t>
+        </is>
+      </c>
+      <c r="D162" s="4" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="E162" s="4" t="inlineStr">
+        <is>
+          <t>Pago</t>
+        </is>
+      </c>
+      <c r="F162" s="4" t="inlineStr">
+        <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="G162" s="4" t="inlineStr">
+        <is>
+          <t>CARTÃO CRÉDITO</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="4" t="inlineStr">
+        <is>
+          <t>Amanda Aragão</t>
+        </is>
+      </c>
+      <c r="B163" s="4" t="inlineStr">
+        <is>
+          <t>591.76</t>
+        </is>
+      </c>
+      <c r="C163" s="4" t="inlineStr">
+        <is>
+          <t>267.458.139-55</t>
+        </is>
+      </c>
+      <c r="D163" s="4" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="E163" s="4" t="inlineStr">
+        <is>
+          <t>Pago</t>
+        </is>
+      </c>
+      <c r="F163" s="4" t="inlineStr">
+        <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="G163" s="4" t="inlineStr">
+        <is>
+          <t>CARTÃO CRÉDITO</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="4" t="inlineStr">
+        <is>
+          <t>Davi Pires</t>
+        </is>
+      </c>
+      <c r="B164" s="4" t="inlineStr">
+        <is>
+          <t>727.04</t>
+        </is>
+      </c>
+      <c r="C164" s="4" t="inlineStr">
+        <is>
+          <t>480.932.617-96</t>
+        </is>
+      </c>
+      <c r="D164" s="4" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="E164" s="4" t="inlineStr">
+        <is>
+          <t>Pago</t>
+        </is>
+      </c>
+      <c r="F164" s="4" t="inlineStr">
+        <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="G164" s="4" t="inlineStr">
+        <is>
+          <t>CARTÃO CRÉDITO</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="4" t="inlineStr">
+        <is>
+          <t>Thiago da Paz</t>
+        </is>
+      </c>
+      <c r="B165" s="4" t="inlineStr">
+        <is>
+          <t>492.14</t>
+        </is>
+      </c>
+      <c r="C165" s="4" t="inlineStr">
+        <is>
+          <t>570.649.381-20</t>
+        </is>
+      </c>
+      <c r="D165" s="4" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="E165" s="4" t="inlineStr">
+        <is>
+          <t>Pago</t>
+        </is>
+      </c>
+      <c r="F165" s="4" t="inlineStr">
+        <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="G165" s="4" t="inlineStr">
+        <is>
+          <t>CARTÃO CRÉDITO</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="4" t="inlineStr">
+        <is>
+          <t>Nina da Rosa</t>
+        </is>
+      </c>
+      <c r="B166" s="4" t="inlineStr">
+        <is>
+          <t>652.92</t>
+        </is>
+      </c>
+      <c r="C166" s="4" t="inlineStr">
+        <is>
+          <t>581.209.374-14</t>
+        </is>
+      </c>
+      <c r="D166" s="4" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="E166" s="4" t="inlineStr">
+        <is>
+          <t>Pago</t>
+        </is>
+      </c>
+      <c r="F166" s="4" t="inlineStr">
+        <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="G166" s="4" t="inlineStr">
+        <is>
+          <t>CARTÃO CRÉDITO</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="4" t="inlineStr">
+        <is>
+          <t>Arthur Alves</t>
+        </is>
+      </c>
+      <c r="B167" s="4" t="inlineStr">
+        <is>
+          <t>912.85</t>
+        </is>
+      </c>
+      <c r="C167" s="4" t="inlineStr">
+        <is>
+          <t>876.510.342-44</t>
+        </is>
+      </c>
+      <c r="D167" s="4" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="E167" s="4" t="inlineStr">
+        <is>
+          <t>Pago</t>
+        </is>
+      </c>
+      <c r="F167" s="4" t="inlineStr">
+        <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="G167" s="4" t="inlineStr">
+        <is>
+          <t>CARTÃO CRÉDITO</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="4" t="inlineStr">
+        <is>
+          <t>Lorena Moraes</t>
+        </is>
+      </c>
+      <c r="B168" s="4" t="inlineStr">
+        <is>
+          <t>697.63</t>
+        </is>
+      </c>
+      <c r="C168" s="4" t="inlineStr">
+        <is>
+          <t>248.731.650-08</t>
+        </is>
+      </c>
+      <c r="D168" s="4" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="E168" s="4" t="inlineStr">
+        <is>
+          <t>Pago</t>
+        </is>
+      </c>
+      <c r="F168" s="4" t="inlineStr">
+        <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="G168" s="4" t="inlineStr">
+        <is>
+          <t>CARTÃO CRÉDITO</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="4" t="inlineStr">
+        <is>
+          <t>Diego Cavalcanti</t>
+        </is>
+      </c>
+      <c r="B169" s="4" t="inlineStr">
+        <is>
+          <t>779.99</t>
+        </is>
+      </c>
+      <c r="C169" s="4" t="inlineStr">
+        <is>
+          <t>861.403.297-87</t>
+        </is>
+      </c>
+      <c r="D169" s="4" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="E169" s="4" t="inlineStr">
+        <is>
+          <t>Pago</t>
+        </is>
+      </c>
+      <c r="F169" s="4" t="inlineStr">
+        <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="G169" s="4" t="inlineStr">
+        <is>
+          <t>CARTÃO CRÉDITO</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="4" t="inlineStr">
+        <is>
+          <t>Ryan Santos</t>
+        </is>
+      </c>
+      <c r="B170" s="4" t="inlineStr">
+        <is>
+          <t>688.38</t>
+        </is>
+      </c>
+      <c r="C170" s="4" t="inlineStr">
+        <is>
+          <t>759.012.864-30</t>
+        </is>
+      </c>
+      <c r="D170" s="4" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="E170" s="4" t="inlineStr">
+        <is>
+          <t>Pago</t>
+        </is>
+      </c>
+      <c r="F170" s="4" t="inlineStr">
+        <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="G170" s="4" t="inlineStr">
+        <is>
+          <t>CARTÃO CRÉDITO</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="4" t="inlineStr">
+        <is>
+          <t>Diogo da Paz</t>
+        </is>
+      </c>
+      <c r="B171" s="4" t="inlineStr">
+        <is>
+          <t>627.28</t>
+        </is>
+      </c>
+      <c r="C171" s="4" t="inlineStr">
+        <is>
+          <t>735.841.926-09</t>
+        </is>
+      </c>
+      <c r="D171" s="4" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="E171" s="4" t="inlineStr">
+        <is>
+          <t>Pago</t>
+        </is>
+      </c>
+      <c r="F171" s="4" t="inlineStr">
+        <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="G171" s="4" t="inlineStr">
+        <is>
+          <t>CARTÃO CRÉDITO</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="4" t="inlineStr">
+        <is>
+          <t>Olivia Pereira</t>
+        </is>
+      </c>
+      <c r="B172" s="4" t="inlineStr">
+        <is>
+          <t>733.57</t>
+        </is>
+      </c>
+      <c r="C172" s="4" t="inlineStr">
+        <is>
+          <t>736.184.092-22</t>
+        </is>
+      </c>
+      <c r="D172" s="4" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="E172" s="4" t="inlineStr">
+        <is>
+          <t>Pago</t>
+        </is>
+      </c>
+      <c r="F172" s="4" t="inlineStr">
+        <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="G172" s="4" t="inlineStr">
+        <is>
+          <t>CARTÃO CRÉDITO</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="4" t="inlineStr">
+        <is>
+          <t>Luiz Gustavo Novaes</t>
+        </is>
+      </c>
+      <c r="B173" s="4" t="inlineStr">
+        <is>
+          <t>424.78</t>
+        </is>
+      </c>
+      <c r="C173" s="4" t="inlineStr">
+        <is>
+          <t>127.384.065-80</t>
+        </is>
+      </c>
+      <c r="D173" s="4" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="E173" s="4" t="inlineStr">
+        <is>
+          <t>Pago</t>
+        </is>
+      </c>
+      <c r="F173" s="4" t="inlineStr">
+        <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="G173" s="4" t="inlineStr">
+        <is>
+          <t>CARTÃO CRÉDITO</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="4" t="inlineStr">
+        <is>
+          <t>Leandro Alves</t>
+        </is>
+      </c>
+      <c r="B174" s="4" t="inlineStr">
+        <is>
+          <t>225.22</t>
+        </is>
+      </c>
+      <c r="C174" s="4" t="inlineStr">
+        <is>
+          <t>947.283.165-64</t>
+        </is>
+      </c>
+      <c r="D174" s="4" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="E174" s="4" t="inlineStr">
+        <is>
+          <t>Pago</t>
+        </is>
+      </c>
+      <c r="F174" s="4" t="inlineStr">
+        <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="G174" s="4" t="inlineStr">
+        <is>
+          <t>CARTÃO CRÉDITO</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="4" t="inlineStr">
+        <is>
+          <t>Raul Freitas</t>
+        </is>
+      </c>
+      <c r="B175" s="4" t="inlineStr">
+        <is>
+          <t>836.42</t>
+        </is>
+      </c>
+      <c r="C175" s="4" t="inlineStr">
+        <is>
+          <t>180.459.673-66</t>
+        </is>
+      </c>
+      <c r="D175" s="4" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="E175" s="4" t="inlineStr">
+        <is>
+          <t>Pago</t>
+        </is>
+      </c>
+      <c r="F175" s="4" t="inlineStr">
+        <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="G175" s="4" t="inlineStr">
+        <is>
+          <t>CARTÃO CRÉDITO</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="4" t="inlineStr">
+        <is>
+          <t>Helena Mendes</t>
+        </is>
+      </c>
+      <c r="B176" s="4" t="inlineStr">
+        <is>
+          <t>531.41</t>
+        </is>
+      </c>
+      <c r="C176" s="4" t="inlineStr">
+        <is>
+          <t>798.462.510-76</t>
+        </is>
+      </c>
+      <c r="D176" s="4" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="E176" s="4" t="inlineStr">
+        <is>
+          <t>Pago</t>
+        </is>
+      </c>
+      <c r="F176" s="4" t="inlineStr">
+        <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="G176" s="4" t="inlineStr">
+        <is>
+          <t>CARTÃO CRÉDITO</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="4" t="inlineStr">
+        <is>
+          <t>Alícia Castro</t>
+        </is>
+      </c>
+      <c r="B177" s="4" t="inlineStr">
+        <is>
+          <t>441.59</t>
+        </is>
+      </c>
+      <c r="C177" s="4" t="inlineStr">
+        <is>
+          <t>326.709.814-96</t>
+        </is>
+      </c>
+      <c r="D177" s="4" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="E177" s="4" t="inlineStr">
+        <is>
+          <t>Pago</t>
+        </is>
+      </c>
+      <c r="F177" s="4" t="inlineStr">
+        <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="G177" s="4" t="inlineStr">
+        <is>
+          <t>CARTÃO CRÉDITO</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="4" t="inlineStr">
+        <is>
+          <t>Augusto Gomes</t>
+        </is>
+      </c>
+      <c r="B178" s="4" t="inlineStr">
+        <is>
+          <t>465.25</t>
+        </is>
+      </c>
+      <c r="C178" s="4" t="inlineStr">
+        <is>
+          <t>867.902.431-78</t>
+        </is>
+      </c>
+      <c r="D178" s="4" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="E178" s="4" t="inlineStr">
+        <is>
+          <t>Pago</t>
+        </is>
+      </c>
+      <c r="F178" s="4" t="inlineStr">
+        <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="G178" s="4" t="inlineStr">
+        <is>
+          <t>CARTÃO CRÉDITO</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="4" t="inlineStr">
+        <is>
+          <t>Pietro Viana</t>
+        </is>
+      </c>
+      <c r="B179" s="4" t="inlineStr">
+        <is>
+          <t>344.26</t>
+        </is>
+      </c>
+      <c r="C179" s="4" t="inlineStr">
+        <is>
+          <t>853.219.047-23</t>
+        </is>
+      </c>
+      <c r="D179" s="4" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="E179" s="4" t="inlineStr">
+        <is>
+          <t>Pago</t>
+        </is>
+      </c>
+      <c r="F179" s="4" t="inlineStr">
+        <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="G179" s="4" t="inlineStr">
+        <is>
+          <t>CARTÃO CRÉDITO</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="4" t="inlineStr">
+        <is>
+          <t>Davi Lucas da Paz</t>
+        </is>
+      </c>
+      <c r="B180" s="4" t="inlineStr">
+        <is>
+          <t>368.93</t>
+        </is>
+      </c>
+      <c r="C180" s="4" t="inlineStr">
+        <is>
+          <t>135.089.726-40</t>
+        </is>
+      </c>
+      <c r="D180" s="4" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="E180" s="4" t="inlineStr">
+        <is>
+          <t>Pago</t>
+        </is>
+      </c>
+      <c r="F180" s="4" t="inlineStr">
+        <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="G180" s="4" t="inlineStr">
+        <is>
+          <t>CARTÃO CRÉDITO</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="4" t="inlineStr">
+        <is>
+          <t>Ana Carolina Aragão</t>
+        </is>
+      </c>
+      <c r="B181" s="4" t="inlineStr">
+        <is>
+          <t>513.12</t>
+        </is>
+      </c>
+      <c r="C181" s="4" t="inlineStr">
+        <is>
+          <t>472.689.135-91</t>
+        </is>
+      </c>
+      <c r="D181" s="4" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="E181" s="4" t="inlineStr">
+        <is>
+          <t>Pago</t>
+        </is>
+      </c>
+      <c r="F181" s="4" t="inlineStr">
+        <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="G181" s="4" t="inlineStr">
+        <is>
+          <t>CARTÃO CRÉDITO</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="4" t="inlineStr">
+        <is>
+          <t>Emilly da Mata</t>
+        </is>
+      </c>
+      <c r="B182" s="4" t="inlineStr">
+        <is>
+          <t>144.28</t>
+        </is>
+      </c>
+      <c r="C182" s="4" t="inlineStr">
+        <is>
+          <t>310.487.569-39</t>
+        </is>
+      </c>
+      <c r="D182" s="4" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="E182" s="4" t="inlineStr">
+        <is>
+          <t>Pago</t>
+        </is>
+      </c>
+      <c r="F182" s="4" t="inlineStr">
+        <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="G182" s="4" t="inlineStr">
+        <is>
+          <t>CARTÃO CRÉDITO</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="4" t="inlineStr">
+        <is>
+          <t>Vicente Costela</t>
+        </is>
+      </c>
+      <c r="B183" s="4" t="inlineStr">
+        <is>
+          <t>518.22</t>
+        </is>
+      </c>
+      <c r="C183" s="4" t="inlineStr">
+        <is>
+          <t>328.059.714-50</t>
+        </is>
+      </c>
+      <c r="D183" s="4" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="E183" s="4" t="inlineStr">
+        <is>
+          <t>Pago</t>
+        </is>
+      </c>
+      <c r="F183" s="4" t="inlineStr">
+        <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="G183" s="4" t="inlineStr">
+        <is>
+          <t>CARTÃO CRÉDITO</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="4" t="inlineStr">
+        <is>
+          <t>Yuri Rezende</t>
+        </is>
+      </c>
+      <c r="B184" s="4" t="inlineStr">
+        <is>
+          <t>155.46</t>
+        </is>
+      </c>
+      <c r="C184" s="4" t="inlineStr">
+        <is>
+          <t>203.598.674-56</t>
+        </is>
+      </c>
+      <c r="D184" s="4" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="E184" s="4" t="inlineStr">
+        <is>
+          <t>Pago</t>
+        </is>
+      </c>
+      <c r="F184" s="4" t="inlineStr">
+        <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="G184" s="4" t="inlineStr">
+        <is>
+          <t>CARTÃO CRÉDITO</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="4" t="inlineStr">
+        <is>
+          <t>Olivia Oliveira</t>
+        </is>
+      </c>
+      <c r="B185" s="4" t="inlineStr">
+        <is>
+          <t>641.42</t>
+        </is>
+      </c>
+      <c r="C185" s="4" t="inlineStr">
+        <is>
+          <t>042.763.518-71</t>
+        </is>
+      </c>
+      <c r="D185" s="4" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="E185" s="4" t="inlineStr">
+        <is>
+          <t>Pago</t>
+        </is>
+      </c>
+      <c r="F185" s="4" t="inlineStr">
+        <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="G185" s="4" t="inlineStr">
+        <is>
+          <t>CARTÃO CRÉDITO</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="4" t="inlineStr">
+        <is>
+          <t>Dr. Renan Novaes</t>
+        </is>
+      </c>
+      <c r="B186" s="4" t="inlineStr">
+        <is>
+          <t>331.03</t>
+        </is>
+      </c>
+      <c r="C186" s="4" t="inlineStr">
+        <is>
+          <t>806.217.439-50</t>
+        </is>
+      </c>
+      <c r="D186" s="4" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="E186" s="4" t="inlineStr">
+        <is>
+          <t>Pago</t>
+        </is>
+      </c>
+      <c r="F186" s="4" t="inlineStr">
+        <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="G186" s="4" t="inlineStr">
+        <is>
+          <t>CARTÃO CRÉDITO</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="4" t="inlineStr">
+        <is>
+          <t>Esther Cavalcanti</t>
+        </is>
+      </c>
+      <c r="B187" s="4" t="inlineStr">
+        <is>
+          <t>555.3</t>
+        </is>
+      </c>
+      <c r="C187" s="4" t="inlineStr">
+        <is>
+          <t>480.562.937-10</t>
+        </is>
+      </c>
+      <c r="D187" s="4" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="E187" s="4" t="inlineStr">
+        <is>
+          <t>Pago</t>
+        </is>
+      </c>
+      <c r="F187" s="4" t="inlineStr">
+        <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="G187" s="4" t="inlineStr">
+        <is>
+          <t>CARTÃO CRÉDITO</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="4" t="inlineStr">
+        <is>
+          <t>Dr. Luiz Fernando Fernandes</t>
+        </is>
+      </c>
+      <c r="B188" s="4" t="inlineStr">
+        <is>
+          <t>664.48</t>
+        </is>
+      </c>
+      <c r="C188" s="4" t="inlineStr">
+        <is>
+          <t>638.907.524-38</t>
+        </is>
+      </c>
+      <c r="D188" s="4" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="E188" s="4" t="inlineStr">
+        <is>
+          <t>Pago</t>
+        </is>
+      </c>
+      <c r="F188" s="4" t="inlineStr">
+        <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="G188" s="4" t="inlineStr">
+        <is>
+          <t>CARTÃO CRÉDITO</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="4" t="inlineStr">
+        <is>
+          <t>Leandro Viana</t>
+        </is>
+      </c>
+      <c r="B189" s="4" t="inlineStr">
+        <is>
+          <t>118.73</t>
+        </is>
+      </c>
+      <c r="C189" s="4" t="inlineStr">
+        <is>
+          <t>781.592.046-20</t>
+        </is>
+      </c>
+      <c r="D189" s="4" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="E189" s="4" t="inlineStr">
+        <is>
+          <t>Pago</t>
+        </is>
+      </c>
+      <c r="F189" s="4" t="inlineStr">
+        <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="G189" s="4" t="inlineStr">
+        <is>
+          <t>CARTÃO CRÉDITO</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="4" t="inlineStr">
+        <is>
+          <t>Carolina Cunha</t>
+        </is>
+      </c>
+      <c r="B190" s="4" t="inlineStr">
+        <is>
+          <t>575.23</t>
+        </is>
+      </c>
+      <c r="C190" s="4" t="inlineStr">
+        <is>
+          <t>094.176.523-70</t>
+        </is>
+      </c>
+      <c r="D190" s="4" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="E190" s="4" t="inlineStr">
+        <is>
+          <t>Pago</t>
+        </is>
+      </c>
+      <c r="F190" s="4" t="inlineStr">
+        <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="G190" s="4" t="inlineStr">
+        <is>
+          <t>CARTÃO CRÉDITO</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="4" t="inlineStr">
+        <is>
+          <t>Lavínia Duarte</t>
+        </is>
+      </c>
+      <c r="B191" s="4" t="inlineStr">
+        <is>
+          <t>283.8</t>
+        </is>
+      </c>
+      <c r="C191" s="4" t="inlineStr">
+        <is>
+          <t>582.493.160-70</t>
+        </is>
+      </c>
+      <c r="D191" s="4" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="E191" s="4" t="inlineStr">
+        <is>
+          <t>Pago</t>
+        </is>
+      </c>
+      <c r="F191" s="4" t="inlineStr">
+        <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="G191" s="4" t="inlineStr">
+        <is>
+          <t>CARTÃO CRÉDITO</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="4" t="inlineStr">
+        <is>
+          <t>Maria Fernanda Costela</t>
+        </is>
+      </c>
+      <c r="B192" s="4" t="inlineStr">
+        <is>
+          <t>134.2</t>
+        </is>
+      </c>
+      <c r="C192" s="4" t="inlineStr">
+        <is>
+          <t>137.602.459-43</t>
+        </is>
+      </c>
+      <c r="D192" s="4" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="E192" s="4" t="inlineStr">
+        <is>
+          <t>Pago</t>
+        </is>
+      </c>
+      <c r="F192" s="4" t="inlineStr">
+        <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="G192" s="4" t="inlineStr">
+        <is>
+          <t>CARTÃO CRÉDITO</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="4" t="inlineStr">
+        <is>
+          <t>Luana Viana</t>
+        </is>
+      </c>
+      <c r="B193" s="4" t="inlineStr">
+        <is>
+          <t>908.58</t>
+        </is>
+      </c>
+      <c r="C193" s="4" t="inlineStr">
+        <is>
+          <t>504.918.276-01</t>
+        </is>
+      </c>
+      <c r="D193" s="4" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="E193" s="4" t="inlineStr">
+        <is>
+          <t>Pago</t>
+        </is>
+      </c>
+      <c r="F193" s="4" t="inlineStr">
+        <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="G193" s="4" t="inlineStr">
+        <is>
+          <t>CARTÃO CRÉDITO</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="4" t="inlineStr">
+        <is>
+          <t>Dr. João Guilherme Caldeira</t>
+        </is>
+      </c>
+      <c r="B194" s="4" t="inlineStr">
+        <is>
+          <t>433.6</t>
+        </is>
+      </c>
+      <c r="C194" s="4" t="inlineStr">
+        <is>
+          <t>509.182.637-86</t>
+        </is>
+      </c>
+      <c r="D194" s="4" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="E194" s="4" t="inlineStr">
+        <is>
+          <t>Pago</t>
+        </is>
+      </c>
+      <c r="F194" s="4" t="inlineStr">
+        <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="G194" s="4" t="inlineStr">
+        <is>
+          <t>CARTÃO CRÉDITO</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="4" t="inlineStr">
+        <is>
+          <t>Maria Vitória Oliveira</t>
+        </is>
+      </c>
+      <c r="B195" s="4" t="inlineStr">
+        <is>
+          <t>312.98</t>
+        </is>
+      </c>
+      <c r="C195" s="4" t="inlineStr">
+        <is>
+          <t>896.342.157-00</t>
+        </is>
+      </c>
+      <c r="D195" s="4" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="E195" s="4" t="inlineStr">
+        <is>
+          <t>Pago</t>
+        </is>
+      </c>
+      <c r="F195" s="4" t="inlineStr">
+        <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="G195" s="4" t="inlineStr">
+        <is>
+          <t>CARTÃO CRÉDITO</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="4" t="inlineStr">
+        <is>
+          <t>Rodrigo das Neves</t>
+        </is>
+      </c>
+      <c r="B196" s="4" t="inlineStr">
+        <is>
+          <t>922.77</t>
+        </is>
+      </c>
+      <c r="C196" s="4" t="inlineStr">
+        <is>
+          <t>975.368.041-48</t>
+        </is>
+      </c>
+      <c r="D196" s="4" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="E196" s="4" t="inlineStr">
+        <is>
+          <t>Pago</t>
+        </is>
+      </c>
+      <c r="F196" s="4" t="inlineStr">
+        <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="G196" s="4" t="inlineStr">
+        <is>
+          <t>CARTÃO CRÉDITO</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="4" t="inlineStr">
+        <is>
+          <t>Maria Alice da Rocha</t>
+        </is>
+      </c>
+      <c r="B197" s="4" t="inlineStr">
+        <is>
+          <t>604.33</t>
+        </is>
+      </c>
+      <c r="C197" s="4" t="inlineStr">
+        <is>
+          <t>341.286.970-87</t>
+        </is>
+      </c>
+      <c r="D197" s="4" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="E197" s="4" t="inlineStr">
+        <is>
+          <t>Pago</t>
+        </is>
+      </c>
+      <c r="F197" s="4" t="inlineStr">
+        <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="G197" s="4" t="inlineStr">
+        <is>
+          <t>CARTÃO CRÉDITO</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>Daniel da Mata</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>736.92</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>593.048.762-65</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>Pago</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>CARTÃO CRÉDITO</t>
         </is>
       </c>
     </row>
